--- a/DataProfiling - Project.xlsx
+++ b/DataProfiling - Project.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\retail-sales-data-visualization-main\retail-sales-data-visualization-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAC947F-DA05-4875-8A01-5CDE19B670B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6149F69-1A17-47F0-9FC7-92376B3A1395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{85F2C9D4-66EC-7B4E-BB51-C1FEF09B4C3A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{85F2C9D4-66EC-7B4E-BB51-C1FEF09B4C3A}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,7 @@
     <sheet name="HandledData" sheetId="5" r:id="rId6"/>
     <sheet name="FinalDataset" sheetId="10" r:id="rId7"/>
     <sheet name="DataAbstraction" sheetId="11" r:id="rId8"/>
-    <sheet name="Sheet1" sheetId="14" r:id="rId9"/>
-    <sheet name="TaskAbstraction" sheetId="12" r:id="rId10"/>
+    <sheet name="TaskAbstraction" sheetId="12" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dataset!$A$1:$J$1075</definedName>
@@ -153,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8726" uniqueCount="1402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8594" uniqueCount="1377">
   <si>
     <t>Transaction ID</t>
   </si>
@@ -4173,129 +4172,6 @@
   </si>
   <si>
     <t>Tổng số tiền của giao dịch</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Dataset: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>final_data</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Item</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>: Mỗi dòng là một giao dịch</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Dataset availability: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Static</t>
-    </r>
-  </si>
-  <si>
-    <t>Số thuộc tính:</t>
-  </si>
-  <si>
-    <t>Sematics</t>
-  </si>
-  <si>
-    <t>Attribute type</t>
-  </si>
-  <si>
-    <t>Hierarchical</t>
-  </si>
-  <si>
-    <t>Characteristic</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Quantiative type</t>
-  </si>
-  <si>
-    <t>Bin number</t>
-  </si>
-  <si>
-    <t>Mã định danh mỗi giao dịch</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Discrete</t>
-  </si>
-  <si>
-    <t>Sequential</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Cyclic</t>
-  </si>
-  <si>
-    <t>Product category</t>
-  </si>
-  <si>
-    <t>Loại sản phẩm</t>
-  </si>
-  <si>
-    <t>Tuổi khách hàng</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>Ngày mà giao dịch được thực hiện</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>Số lượng sản phẩm được mua trong giao dịch</t>
   </si>
   <si>
     <t>1. Context: Dataset Recap</t>
@@ -4759,7 +4635,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4853,30 +4729,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="15">
@@ -5157,7 +5009,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5237,35 +5089,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -40319,7 +40165,7 @@
         <v>75</v>
       </c>
       <c r="J1026" s="1" t="str">
-        <f t="shared" ref="J1026:J1089" si="16">IF(G1026*H1026=I1026,"ok","ko")</f>
+        <f t="shared" ref="J1026:J1075" si="16">IF(G1026*H1026=I1026,"ok","ko")</f>
         <v>ok</v>
       </c>
     </row>
@@ -42034,231 +41880,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BABB412-D040-4162-B23D-F98EBEEE20B8}">
-  <dimension ref="A1:B55"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
-  <sheetData>
-    <row r="1" spans="1:2" ht="23.4">
-      <c r="A1" s="61" t="s">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="60" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="60" t="s">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="60" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="23.4">
-      <c r="A7" s="61" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="60" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="B9" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="60" t="s">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="B11" t="s">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="60" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="B13" t="s">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="60" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="B15" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="23.4">
-      <c r="A17" s="61" t="s">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="60" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="B19" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="60" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="B23" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="B25" t="s">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="60" t="s">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="B30" t="s">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="B32" t="s">
-        <v>1381</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="23.4">
-      <c r="A34" s="61" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="60" t="s">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="60" t="s">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="60" t="s">
-        <v>1385</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="23.4">
-      <c r="A39" s="61" t="s">
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="60" t="s">
-        <v>1387</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="60" t="s">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="60" t="s">
-        <v>1389</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="60" t="s">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="23.4">
-      <c r="A45" s="61" t="s">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="60" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="B47" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="60" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="B49" t="s">
-        <v>1395</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="60" t="s">
-        <v>1396</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="B51" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="60" t="s">
-        <v>1398</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="B53" t="s">
-        <v>1399</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="60" t="s">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="B55" t="s">
-        <v>1401</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D9E7BFE-5D14-0A41-9C96-284881578C5F}">
   <dimension ref="A1:H10"/>
@@ -42612,10 +42233,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="65" t="s">
         <v>1253</v>
       </c>
-      <c r="B1" s="70"/>
+      <c r="B1" s="65"/>
       <c r="C1" s="9" t="s">
         <v>1254</v>
       </c>
@@ -42625,10 +42246,10 @@
       <c r="E1" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="G1" s="70" t="s">
+      <c r="G1" s="65" t="s">
         <v>1253</v>
       </c>
-      <c r="H1" s="70"/>
+      <c r="H1" s="65"/>
       <c r="I1" s="9" t="s">
         <v>1257</v>
       </c>
@@ -42748,10 +42369,10 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="65" t="s">
         <v>1263</v>
       </c>
-      <c r="B5" s="70"/>
+      <c r="B5" s="65"/>
       <c r="C5" s="7" t="s">
         <v>1264</v>
       </c>
@@ -42763,10 +42384,10 @@
         <f t="shared" si="0"/>
         <v>1.5828677839851025E-2</v>
       </c>
-      <c r="G5" s="70" t="s">
+      <c r="G5" s="65" t="s">
         <v>1265</v>
       </c>
-      <c r="H5" s="70"/>
+      <c r="H5" s="65"/>
       <c r="I5" s="7">
         <v>54</v>
       </c>
@@ -42976,14 +42597,14 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="69" t="s">
         <v>1266</v>
       </c>
-      <c r="B13" s="71"/>
-      <c r="G13" s="71" t="s">
+      <c r="B13" s="69"/>
+      <c r="G13" s="69" t="s">
         <v>1266</v>
       </c>
-      <c r="H13" s="71"/>
+      <c r="H13" s="69"/>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="10" t="s">
@@ -43070,16 +42691,16 @@
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="72"/>
-      <c r="B20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
+      <c r="A20" s="64"/>
+      <c r="B20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="70" t="s">
+      <c r="A26" s="65" t="s">
         <v>1253</v>
       </c>
-      <c r="B26" s="70"/>
+      <c r="B26" s="65"/>
       <c r="C26" s="9" t="s">
         <v>1275</v>
       </c>
@@ -43089,10 +42710,10 @@
       <c r="E26" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="G26" s="70" t="s">
+      <c r="G26" s="65" t="s">
         <v>1253</v>
       </c>
-      <c r="H26" s="70"/>
+      <c r="H26" s="65"/>
       <c r="I26" s="9" t="s">
         <v>1276</v>
       </c>
@@ -43209,17 +42830,17 @@
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="70" t="s">
+      <c r="A30" s="65" t="s">
         <v>1265</v>
       </c>
-      <c r="B30" s="70"/>
+      <c r="B30" s="65"/>
       <c r="C30" s="7"/>
       <c r="D30" s="4"/>
       <c r="E30" s="6"/>
-      <c r="G30" s="70" t="s">
+      <c r="G30" s="65" t="s">
         <v>1265</v>
       </c>
-      <c r="H30" s="70"/>
+      <c r="H30" s="65"/>
       <c r="I30" s="7">
         <v>4</v>
       </c>
@@ -43422,14 +43043,14 @@
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="71" t="s">
+      <c r="A38" s="69" t="s">
         <v>1266</v>
       </c>
-      <c r="B38" s="71"/>
-      <c r="G38" s="71" t="s">
+      <c r="B38" s="69"/>
+      <c r="G38" s="69" t="s">
         <v>1266</v>
       </c>
-      <c r="H38" s="71"/>
+      <c r="H38" s="69"/>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="10" t="s">
@@ -43516,16 +43137,16 @@
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="72"/>
-      <c r="B45" s="72"/>
-      <c r="G45" s="72"/>
-      <c r="H45" s="72"/>
+      <c r="A45" s="64"/>
+      <c r="B45" s="64"/>
+      <c r="G45" s="64"/>
+      <c r="H45" s="64"/>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="70" t="s">
+      <c r="A51" s="65" t="s">
         <v>1253</v>
       </c>
-      <c r="B51" s="70"/>
+      <c r="B51" s="65"/>
       <c r="C51" s="37" t="s">
         <v>1280</v>
       </c>
@@ -43535,10 +43156,10 @@
       <c r="E51" s="38" t="s">
         <v>1256</v>
       </c>
-      <c r="G51" s="70" t="s">
+      <c r="G51" s="65" t="s">
         <v>1253</v>
       </c>
-      <c r="H51" s="70"/>
+      <c r="H51" s="65"/>
       <c r="I51" s="9" t="s">
         <v>1281</v>
       </c>
@@ -43652,10 +43273,10 @@
       </c>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="70" t="s">
+      <c r="A55" s="65" t="s">
         <v>1265</v>
       </c>
-      <c r="B55" s="73"/>
+      <c r="B55" s="66"/>
       <c r="C55" s="33">
         <v>45048</v>
       </c>
@@ -43666,10 +43287,10 @@
         <f t="shared" si="4"/>
         <v>7.4487895716945996E-3</v>
       </c>
-      <c r="G55" s="70" t="s">
+      <c r="G55" s="65" t="s">
         <v>1265</v>
       </c>
-      <c r="H55" s="70"/>
+      <c r="H55" s="65"/>
       <c r="I55" s="7" t="s">
         <v>864</v>
       </c>
@@ -43914,14 +43535,14 @@
       </c>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="71" t="s">
+      <c r="A63" s="69" t="s">
         <v>1266</v>
       </c>
-      <c r="B63" s="71"/>
-      <c r="G63" s="71" t="s">
+      <c r="B63" s="69"/>
+      <c r="G63" s="69" t="s">
         <v>1266</v>
       </c>
-      <c r="H63" s="71"/>
+      <c r="H63" s="69"/>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="10" t="s">
@@ -44008,16 +43629,16 @@
       </c>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="72"/>
-      <c r="B70" s="72"/>
-      <c r="G70" s="72"/>
-      <c r="H70" s="72"/>
+      <c r="A70" s="64"/>
+      <c r="B70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="70" t="s">
+      <c r="A76" s="65" t="s">
         <v>1253</v>
       </c>
-      <c r="B76" s="70"/>
+      <c r="B76" s="65"/>
       <c r="C76" s="9" t="s">
         <v>1283</v>
       </c>
@@ -44027,10 +43648,10 @@
       <c r="E76" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="G76" s="70" t="s">
+      <c r="G76" s="65" t="s">
         <v>1253</v>
       </c>
-      <c r="H76" s="70"/>
+      <c r="H76" s="65"/>
       <c r="I76" s="9" t="s">
         <v>1284</v>
       </c>
@@ -44150,10 +43771,10 @@
       </c>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="70" t="s">
+      <c r="A80" s="65" t="s">
         <v>1263</v>
       </c>
-      <c r="B80" s="70"/>
+      <c r="B80" s="65"/>
       <c r="C80" s="7">
         <v>3</v>
       </c>
@@ -44165,10 +43786,10 @@
         <f>D80/1074</f>
         <v>0.22998137802607077</v>
       </c>
-      <c r="G80" s="70" t="s">
+      <c r="G80" s="65" t="s">
         <v>1263</v>
       </c>
-      <c r="H80" s="70"/>
+      <c r="H80" s="65"/>
       <c r="I80" s="7">
         <v>300</v>
       </c>
@@ -44245,9 +43866,9 @@
         <f>DatasetSumary!$C9</f>
         <v>0</v>
       </c>
-      <c r="I82" s="74"/>
-      <c r="J82" s="75"/>
-      <c r="K82" s="75"/>
+      <c r="I82" s="70"/>
+      <c r="J82" s="71"/>
+      <c r="K82" s="71"/>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="4" t="s">
@@ -44257,9 +43878,9 @@
         <f>DatasetSumary!$D8</f>
         <v>1074</v>
       </c>
-      <c r="C83" s="74"/>
-      <c r="D83" s="75"/>
-      <c r="E83" s="75"/>
+      <c r="C83" s="70"/>
+      <c r="D83" s="71"/>
+      <c r="E83" s="71"/>
       <c r="G83" s="4" t="s">
         <v>1248</v>
       </c>
@@ -44333,14 +43954,14 @@
       </c>
     </row>
     <row r="88" spans="1:11">
-      <c r="A88" s="71" t="s">
+      <c r="A88" s="69" t="s">
         <v>1266</v>
       </c>
-      <c r="B88" s="71"/>
-      <c r="G88" s="71" t="s">
+      <c r="B88" s="69"/>
+      <c r="G88" s="69" t="s">
         <v>1266</v>
       </c>
-      <c r="H88" s="71"/>
+      <c r="H88" s="69"/>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="10" t="s">
@@ -44427,16 +44048,16 @@
       </c>
     </row>
     <row r="95" spans="1:11">
-      <c r="A95" s="72"/>
-      <c r="B95" s="72"/>
-      <c r="G95" s="72"/>
-      <c r="H95" s="72"/>
+      <c r="A95" s="64"/>
+      <c r="B95" s="64"/>
+      <c r="G95" s="64"/>
+      <c r="H95" s="64"/>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="70" t="s">
+      <c r="A101" s="65" t="s">
         <v>1253</v>
       </c>
-      <c r="B101" s="70"/>
+      <c r="B101" s="65"/>
       <c r="C101" s="37" t="s">
         <v>1285</v>
       </c>
@@ -44505,10 +44126,10 @@
       </c>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="70" t="s">
+      <c r="A105" s="65" t="s">
         <v>1263</v>
       </c>
-      <c r="B105" s="73"/>
+      <c r="B105" s="66"/>
       <c r="C105" s="10">
         <v>1200</v>
       </c>
@@ -44649,15 +44270,15 @@
         <f>DatasetSumary!$H10</f>
         <v>1.6759776536312849E-2</v>
       </c>
-      <c r="C112" s="76"/>
-      <c r="D112" s="77"/>
-      <c r="E112" s="77"/>
+      <c r="C112" s="67"/>
+      <c r="D112" s="68"/>
+      <c r="E112" s="68"/>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="71" t="s">
+      <c r="A113" s="69" t="s">
         <v>1266</v>
       </c>
-      <c r="B113" s="71"/>
+      <c r="B113" s="69"/>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="10" t="s">
@@ -44708,22 +44329,27 @@
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="72"/>
-      <c r="B120" s="72"/>
+      <c r="A120" s="64"/>
+      <c r="B120" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A120:B120"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G51:H51"/>
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="A95:B95"/>
@@ -44736,22 +44362,17 @@
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="A76:B76"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="A113:B113"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -44776,17 +44397,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="72" t="s">
         <v>1286</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
       <c r="K1" s="14" t="s">
         <v>1287</v>
       </c>
@@ -45236,10 +44857,10 @@
       <c r="I1" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="79" t="s">
+      <c r="K1" s="73" t="s">
         <v>1290</v>
       </c>
-      <c r="L1" s="79"/>
+      <c r="L1" s="73"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
       <c r="A2" s="42">
@@ -46964,13 +46585,13 @@
       <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="81" t="s">
+      <c r="K1" s="75" t="s">
         <v>1247</v>
       </c>
-      <c r="L1" s="83" t="s">
+      <c r="L1" s="77" t="s">
         <v>1294</v>
       </c>
-      <c r="M1" s="83"/>
+      <c r="M1" s="77"/>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="42">
@@ -47001,7 +46622,7 @@
         <f>$G2*$H2</f>
         <v>120</v>
       </c>
-      <c r="K2" s="81"/>
+      <c r="K2" s="75"/>
       <c r="L2" s="10" t="s">
         <v>1295</v>
       </c>
@@ -47036,7 +46657,7 @@
         <f>$G3*$H3</f>
         <v>25</v>
       </c>
-      <c r="K3" s="81"/>
+      <c r="K3" s="75"/>
       <c r="L3" s="10" t="s">
         <v>1296</v>
       </c>
@@ -47070,11 +46691,11 @@
       <c r="I4" s="56">
         <v>2500</v>
       </c>
-      <c r="K4" s="81"/>
-      <c r="L4" s="83" t="s">
+      <c r="K4" s="75"/>
+      <c r="L4" s="77" t="s">
         <v>1297</v>
       </c>
-      <c r="M4" s="83"/>
+      <c r="M4" s="77"/>
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="42">
@@ -47104,7 +46725,7 @@
       <c r="I5" s="42">
         <v>1000</v>
       </c>
-      <c r="K5" s="81"/>
+      <c r="K5" s="75"/>
       <c r="L5" s="10" t="s">
         <v>1298</v>
       </c>
@@ -47138,7 +46759,7 @@
       <c r="I6" s="42">
         <v>100</v>
       </c>
-      <c r="K6" s="81"/>
+      <c r="K6" s="75"/>
       <c r="L6" s="10" t="s">
         <v>1299</v>
       </c>
@@ -47172,7 +46793,7 @@
       <c r="I7" s="56">
         <v>180</v>
       </c>
-      <c r="K7" s="82"/>
+      <c r="K7" s="76"/>
       <c r="L7" s="22" t="s">
         <v>1300</v>
       </c>
@@ -47206,13 +46827,13 @@
       <c r="I8" s="42">
         <v>100</v>
       </c>
-      <c r="K8" s="84" t="s">
+      <c r="K8" s="78" t="s">
         <v>1301</v>
       </c>
-      <c r="L8" s="83" t="s">
+      <c r="L8" s="77" t="s">
         <v>1294</v>
       </c>
-      <c r="M8" s="83"/>
+      <c r="M8" s="77"/>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="42">
@@ -47242,7 +46863,7 @@
       <c r="I9" s="42">
         <v>100</v>
       </c>
-      <c r="K9" s="84"/>
+      <c r="K9" s="78"/>
       <c r="L9" s="10" t="s">
         <v>1295</v>
       </c>
@@ -47276,7 +46897,7 @@
       <c r="I10" s="42">
         <v>50</v>
       </c>
-      <c r="K10" s="84"/>
+      <c r="K10" s="78"/>
       <c r="L10" s="10" t="s">
         <v>1296</v>
       </c>
@@ -47310,11 +46931,11 @@
       <c r="I11" s="42">
         <v>500</v>
       </c>
-      <c r="K11" s="84"/>
-      <c r="L11" s="83" t="s">
+      <c r="K11" s="78"/>
+      <c r="L11" s="77" t="s">
         <v>1297</v>
       </c>
-      <c r="M11" s="83"/>
+      <c r="M11" s="77"/>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" s="42">
@@ -47344,7 +46965,7 @@
       <c r="I12" s="42">
         <v>300</v>
       </c>
-      <c r="K12" s="84"/>
+      <c r="K12" s="78"/>
       <c r="L12" s="10" t="s">
         <v>1302</v>
       </c>
@@ -47378,7 +46999,7 @@
       <c r="I13" s="56">
         <v>180</v>
       </c>
-      <c r="K13" s="84"/>
+      <c r="K13" s="78"/>
       <c r="L13" s="10" t="s">
         <v>1303</v>
       </c>
@@ -47441,17 +47062,17 @@
       <c r="I15" s="56">
         <v>125</v>
       </c>
-      <c r="O15" s="80" t="s">
+      <c r="O15" s="74" t="s">
         <v>1304</v>
       </c>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="80"/>
-      <c r="S15" s="80"/>
-      <c r="T15" s="80"/>
-      <c r="U15" s="80"/>
-      <c r="V15" s="80"/>
-      <c r="W15" s="80"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="74"/>
+      <c r="T15" s="74"/>
+      <c r="U15" s="74"/>
+      <c r="V15" s="74"/>
+      <c r="W15" s="74"/>
     </row>
     <row r="16" spans="1:23">
       <c r="A16" s="42">
@@ -49365,7 +48986,7 @@
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="63" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
@@ -80824,569 +80445,224 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA80311-F517-43E6-A139-7E3C151AA411}">
-  <dimension ref="B6:I54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BABB412-D040-4162-B23D-F98EBEEE20B8}">
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
-  <cols>
-    <col min="2" max="2" width="14.8984375" customWidth="1"/>
-    <col min="3" max="3" width="39.19921875" customWidth="1"/>
-    <col min="4" max="4" width="14.19921875" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="13.3984375" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="16.5" customWidth="1"/>
-    <col min="9" max="9" width="10.69921875" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="6" spans="2:9">
-      <c r="B6" s="66" t="s">
+    <row r="1" spans="1:2" ht="23.4">
+      <c r="A1" s="61" t="s">
         <v>1334</v>
       </c>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" s="65" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="60" t="s">
         <v>1335</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" s="66" t="s">
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="60" t="s">
         <v>1336</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" s="63" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="60" t="s">
         <v>1337</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="B11" s="67" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C11" s="67" t="s">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>1338</v>
       </c>
-      <c r="D11" s="67" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="23.4">
+      <c r="A7" s="61" t="s">
         <v>1339</v>
       </c>
-      <c r="E11" s="67" t="s">
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="60" t="s">
         <v>1340</v>
       </c>
-      <c r="F11" s="68" t="s">
+    </row>
+    <row r="9" spans="1:2">
+      <c r="B9" t="s">
         <v>1341</v>
       </c>
-      <c r="G11" s="68" t="s">
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="60" t="s">
         <v>1342</v>
       </c>
-      <c r="H11" s="68" t="s">
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" t="s">
         <v>1343</v>
       </c>
-      <c r="I11" s="68" t="s">
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="60" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="12" spans="2:9">
-      <c r="B12" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="10" t="s">
+    <row r="13" spans="1:2">
+      <c r="B13" t="s">
         <v>1345</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>1325</v>
-      </c>
-      <c r="E12" s="10" t="s">
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="60" t="s">
         <v>1346</v>
       </c>
-      <c r="F12" s="10" t="s">
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
         <v>1347</v>
       </c>
-      <c r="G12" s="10" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="23.4">
+      <c r="A17" s="61" t="s">
         <v>1348</v>
       </c>
-      <c r="H12" s="10" t="s">
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="60" t="s">
         <v>1349</v>
       </c>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="B13" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>1324</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>1317</v>
-      </c>
-      <c r="E13" s="10" t="s">
+    </row>
+    <row r="19" spans="1:2">
+      <c r="B19" t="s">
         <v>1350</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G13" s="10" t="s">
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="60" t="s">
         <v>1351</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>1319</v>
-      </c>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="66" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="65" t="s">
-        <v>1335</v>
-      </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="66" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="63" t="s">
-        <v>1337</v>
-      </c>
-      <c r="C24" s="63"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" s="64"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="67" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C26" s="67" t="s">
-        <v>1338</v>
-      </c>
-      <c r="D26" s="67" t="s">
-        <v>1339</v>
-      </c>
-      <c r="E26" s="67" t="s">
-        <v>1340</v>
-      </c>
-      <c r="F26" s="68" t="s">
-        <v>1341</v>
-      </c>
-      <c r="G26" s="68" t="s">
-        <v>1342</v>
-      </c>
-      <c r="H26" s="68" t="s">
-        <v>1343</v>
-      </c>
-      <c r="I26" s="68" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>1345</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>1325</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>1348</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>1349</v>
-      </c>
-      <c r="I27" s="10"/>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="10" t="s">
+    </row>
+    <row r="23" spans="1:2">
+      <c r="B23" t="s">
         <v>1352</v>
       </c>
-      <c r="C28" s="10" t="s">
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" t="s">
         <v>1353</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>1325</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>1349</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>1349</v>
-      </c>
-      <c r="I28" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>1327</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>1325</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>1349</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>1349</v>
-      </c>
-      <c r="I29" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="10" t="s">
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="60" t="s">
         <v>1354</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>1317</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F30" s="10" t="s">
+    </row>
+    <row r="30" spans="1:2">
+      <c r="B30" t="s">
         <v>1355</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>1348</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>1328</v>
-      </c>
-      <c r="I30" s="10"/>
-    </row>
-    <row r="34" spans="2:9">
-      <c r="B34" s="66" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-    </row>
-    <row r="35" spans="2:9">
-      <c r="B35" s="65" t="s">
-        <v>1335</v>
-      </c>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-    </row>
-    <row r="36" spans="2:9">
-      <c r="B36" s="66" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C36" s="64"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-    </row>
-    <row r="37" spans="2:9">
-      <c r="B37" s="63" t="s">
-        <v>1337</v>
-      </c>
-      <c r="C37" s="63"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
-    </row>
-    <row r="38" spans="2:9">
-      <c r="B38" s="64"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-    </row>
-    <row r="39" spans="2:9">
-      <c r="B39" s="67" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C39" s="67" t="s">
-        <v>1338</v>
-      </c>
-      <c r="D39" s="67" t="s">
-        <v>1339</v>
-      </c>
-      <c r="E39" s="67" t="s">
-        <v>1340</v>
-      </c>
-      <c r="F39" s="68" t="s">
-        <v>1341</v>
-      </c>
-      <c r="G39" s="68" t="s">
-        <v>1342</v>
-      </c>
-      <c r="H39" s="68" t="s">
-        <v>1343</v>
-      </c>
-      <c r="I39" s="68" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>1327</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>1325</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>1349</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>1349</v>
-      </c>
-      <c r="I40" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9">
-      <c r="B41" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>1317</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>1355</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>1348</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>1328</v>
-      </c>
-      <c r="I41" s="10"/>
-    </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>1317</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>1348</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>1328</v>
-      </c>
-      <c r="I42" s="10"/>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="B46" s="66" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-    </row>
-    <row r="47" spans="2:9">
-      <c r="B47" s="65" t="s">
-        <v>1335</v>
-      </c>
-      <c r="C47" s="64"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="64"/>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="B48" s="66" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C48" s="64"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
-    </row>
-    <row r="49" spans="2:9">
-      <c r="B49" s="63" t="s">
-        <v>1337</v>
-      </c>
-      <c r="C49" s="63"/>
-      <c r="D49" s="64"/>
-      <c r="E49" s="64"/>
-    </row>
-    <row r="50" spans="2:9">
-      <c r="B50" s="64"/>
-      <c r="C50" s="64"/>
-      <c r="D50" s="64"/>
-      <c r="E50" s="64"/>
-    </row>
-    <row r="51" spans="2:9">
-      <c r="B51" s="67" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C51" s="67" t="s">
-        <v>1338</v>
-      </c>
-      <c r="D51" s="67" t="s">
-        <v>1339</v>
-      </c>
-      <c r="E51" s="67" t="s">
-        <v>1340</v>
-      </c>
-      <c r="F51" s="68" t="s">
-        <v>1341</v>
-      </c>
-      <c r="G51" s="68" t="s">
-        <v>1342</v>
-      </c>
-      <c r="H51" s="68" t="s">
-        <v>1343</v>
-      </c>
-      <c r="I51" s="68" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9">
-      <c r="B52" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="10" t="s">
+    </row>
+    <row r="32" spans="1:2">
+      <c r="B32" t="s">
         <v>1356</v>
       </c>
-      <c r="D52" s="10" t="s">
+    </row>
+    <row r="34" spans="1:2" ht="23.4">
+      <c r="A34" s="61" t="s">
         <v>1357</v>
       </c>
-      <c r="E52" s="10" t="s">
-        <v>1350</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>1355</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>1351</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>1319</v>
-      </c>
-      <c r="I52" s="10"/>
-    </row>
-    <row r="53" spans="2:9">
-      <c r="B53" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>1317</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>1348</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>1328</v>
-      </c>
-      <c r="I53" s="10"/>
-    </row>
-    <row r="54" spans="2:9">
-      <c r="B54" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="10" t="s">
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="60" t="s">
         <v>1358</v>
       </c>
-      <c r="D54" s="10" t="s">
-        <v>1317</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F54" s="10" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>1348</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>1328</v>
-      </c>
-      <c r="I54" s="10"/>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="60" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="60" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="23.4">
+      <c r="A39" s="61" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="60" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="60" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="60" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="60" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="23.4">
+      <c r="A45" s="61" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="60" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="B47" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="60" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="B49" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="60" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="B51" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="60" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="B53" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="60" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="B55" t="s">
+        <v>1376</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
